--- a/output/HS_Code_Summary_Adventure_Guy_2026100076281_2026100076288.xlsx
+++ b/output/HS_Code_Summary_Adventure_Guy_2026100076281_2026100076288.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="HS Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Detail dle faktur" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dokumenty a poznámky" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Rozpočet hmotnosti" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dokumenty a poznámky" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,11 +32,19 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <i val="1"/>
@@ -43,12 +54,17 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -92,31 +108,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -581,15 +609,13 @@
       <c r="E2" s="2" t="n">
         <v>143</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
+      <c r="F2" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A2,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
+        <v/>
+      </c>
+      <c r="G2" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A2,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
+        <v/>
       </c>
       <c r="H2" s="4" t="n">
         <v>1105</v>
@@ -629,15 +655,13 @@
       <c r="E3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
+      <c r="F3" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A3,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
+        <v/>
+      </c>
+      <c r="G3" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A3,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
+        <v/>
       </c>
       <c r="H3" s="4" t="n">
         <v>300</v>
@@ -673,15 +697,13 @@
       <c r="E4" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
+      <c r="F4" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A4,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
+        <v/>
+      </c>
+      <c r="G4" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A4,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
+        <v/>
       </c>
       <c r="H4" s="4" t="n">
         <v>80</v>
@@ -713,15 +735,13 @@
       <c r="E5" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
+      <c r="F5" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A5,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
+        <v/>
+      </c>
+      <c r="G5" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A5,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
+        <v/>
       </c>
       <c r="H5" s="4" t="n">
         <v>70</v>
@@ -761,15 +781,13 @@
       <c r="E6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
+      <c r="F6" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A6,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
+        <v/>
+      </c>
+      <c r="G6" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A6,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
+        <v/>
       </c>
       <c r="H6" s="4" t="n">
         <v>35</v>
@@ -805,15 +823,13 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
+      <c r="F7" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A7,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
+        <v/>
+      </c>
+      <c r="G7" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A7,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
+        <v/>
       </c>
       <c r="H7" s="4" t="n">
         <v>30</v>
@@ -849,15 +865,13 @@
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
+      <c r="F8" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A8,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
+        <v/>
+      </c>
+      <c r="G8" s="3">
+        <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A8,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
+        <v/>
       </c>
       <c r="H8" s="4" t="n">
         <v>2</v>
@@ -877,15 +891,13 @@
       <c r="E9" s="6" t="n">
         <v>266</v>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
+      <c r="F9" s="7">
+        <f>SUM(F2:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="7">
+        <f>SUM(G2:G8)</f>
+        <v/>
       </c>
       <c r="H9" s="7" t="n">
         <v>1622</v>
@@ -904,60 +916,60 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>🟡 ŽLUTÁ</t>
+          <t>🟢 ZELENÁ</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Údaj chybí v podkladech nebo zařazení vyžaduje potvrzení – viz sloupec poznámky.</t>
+          <t>Hmotnost dopočtena – viz list „Rozpočet hmotnosti“. Kotvena na hrubou hmotnost 974 kg z BL; rozpad na kódy KN je kvalifikovaný odhad.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>🟡 ŽLUTÁ</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>V zásilce NENÍ žádná položka podléhající CBAM – žádný z uvedených kódů KN není v příloze I nařízení CBAM. Detail viz list „Dokumenty a poznámky“.</t>
+          <t>Zařazení vyžaduje potvrzení – viz sloupec poznámky.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Antidumping</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Žádná z položek nepodléhá antidumpingovému clu (původ US).</t>
+          <t>V zásilce NENÍ žádná položka podléhající CBAM – žádný z uvedených kódů KN není v příloze I nařízení CBAM. Detail viz list „Dokumenty a poznámky“.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Incoterm</t>
+          <t>Antidumping</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>EXW – faktury neuvádějí místo dodání. Ověřit s odesílatelem (pravděpodobně EXW Groveport, OH). Viz poznámky.</t>
+          <t>Žádná z položek nepodléhá antidumpingovému clu (původ US).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Hmotnosti</t>
+          <t>Incoterm</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Čistá ani hrubá hmotnost NEJSOU v žádném z dodaných dokladů uvedeny – nutno doplnit od odesílatele/dopravce.</t>
+          <t>EXW – faktury neuvádějí místo dodání. Ověřit s odesílatelem (pravděpodobně EXW Groveport, OH). Viz poznámky.</t>
         </is>
       </c>
     </row>
@@ -984,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -992,9 +1004,10 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1025,15 +1038,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Kartony</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>HTS kód (US, dle faktury)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>HS kód (KN 2026, pro JSD)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Hodnota USD</t>
         </is>
@@ -1063,17 +1081,20 @@
       <c r="E2" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>4908.90.5060</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1101,17 +1122,20 @@
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>8310.00.0000</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>8310 00 00</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1139,17 +1163,20 @@
       <c r="E4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5702.32.10.00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5702 42 00</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1177,17 +1204,20 @@
       <c r="E5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>9403.20.00.86</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>9403 99 10</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1215,17 +1245,20 @@
       <c r="E6" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>9403.60.0000</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9403 60 30</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1253,17 +1286,20 @@
       <c r="E7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>3920.43.0000</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1291,17 +1327,20 @@
       <c r="E8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>4823.90.8600</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1329,17 +1368,20 @@
       <c r="E9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>3920.43.0000</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1367,17 +1409,20 @@
       <c r="E10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>3920.43.0000</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1405,17 +1450,20 @@
       <c r="E11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>3920.43.0000</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1443,17 +1491,20 @@
       <c r="E12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>4823.90.8600</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1481,17 +1532,20 @@
       <c r="E13" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>5702.32.10.00</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5702 42 00</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1519,17 +1573,20 @@
       <c r="E14" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>9618.00.00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9618 00 00</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="I14" s="4" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1557,17 +1614,20 @@
       <c r="E15" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>9618.00.00</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>9618 00 00</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1595,17 +1655,20 @@
       <c r="E16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>3920.43.0000</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1633,17 +1696,20 @@
       <c r="E17" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>9403.20.00.86</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>9403 20 80</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="I17" s="4" t="n">
         <v>200</v>
       </c>
     </row>
@@ -1671,17 +1737,20 @@
       <c r="E18" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>9403.20.00.86</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>9403 20 80</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="I18" s="4" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1709,17 +1778,20 @@
       <c r="E19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>9403.20.00.86</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>9403 99 10</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="I19" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1747,17 +1819,20 @@
       <c r="E20" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>4908.90.5060</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="I20" s="4" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1773,16 +1848,26 @@
       <c r="E21" s="6" t="n">
         <v>266</v>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="n">
+        <v>134</v>
+      </c>
       <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="7" t="n">
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="7" t="n">
         <v>1622</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Žlutě: US HTS kód na faktuře se liší od kódu KN použitého pro dovozní JSD (běžná odchylka US HTS vs. EU KN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Kartony načteny z packing slipů podle jedinečných čísel SSCC – celkem 134 kartonů (7 + 127).</t>
         </is>
       </c>
     </row>
@@ -1797,361 +1882,1296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A57"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>ROZPOČET HMOTNOSTI NA KÓDY KN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Celková hrubá hmotnost dle BL (kg)</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="n">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Součet odhadů (kg)</t>
+        </is>
+      </c>
+      <c r="B3" s="13">
+        <f>SUM(G11:G27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Přepočtový faktor (BL / součet odhadů)</t>
+        </is>
+      </c>
+      <c r="B4" s="14">
+        <f>B2/B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Faktor obalu (hrubá / čistá)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Celková čistá hmotnost (kg)</t>
+        </is>
+      </c>
+      <c r="B6" s="13">
+        <f>SUM(I11:I27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>VSTUPNÍ ÚDAJ K ÚPRAVĚ: sloupec F (odhad jednotkové hmotnosti). Přepiš hodnoty podle skutečnosti – součet se vždy automaticky dorovná na hrubou hmotnost 974 kg z BL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Název</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>HS kód (KN 2026)</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Množství (ks)</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Kartony</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Odhad jedn. hrubé hmotnosti (kg/ks)</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Odhad celkem (kg)</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>Hrubá hmotnost po dorovnání (kg)</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Čistá hmotnost (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>9002_DARN</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>DTV Stickers - 100 Pack</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4911 10 90</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G11" s="4">
+        <f>D11*F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="4">
+        <f>G11*$B$4</f>
+        <v/>
+      </c>
+      <c r="I11" s="4">
+        <f>H11/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>9179_DARN</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Willoughby (25 Pack)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4911 10 90</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G12" s="4">
+        <f>D12*F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="4">
+        <f>G12*$B$4</f>
+        <v/>
+      </c>
+      <c r="I12" s="4">
+        <f>H12/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>9093_DARN</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Med/Large Tactical Retail Header</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4911 10 90</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G13" s="4">
+        <f>D13*F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="4">
+        <f>G13*$B$4</f>
+        <v/>
+      </c>
+      <c r="I13" s="4">
+        <f>H13/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>9121_DARN</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Medium Rack Header - Hike/Trek</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4911 10 90</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G14" s="4">
+        <f>D14*F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="4">
+        <f>G14*$B$4</f>
+        <v/>
+      </c>
+      <c r="I14" s="4">
+        <f>H14/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>9122_DARN</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Medium Rack Header - Snow</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4911 10 90</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G15" s="4">
+        <f>D15*F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="4">
+        <f>G15*$B$4</f>
+        <v/>
+      </c>
+      <c r="I15" s="4">
+        <f>H15/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>9125_DARN</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Medium Rack Header - Work</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4911 10 90</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G16" s="4">
+        <f>D16*F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="4">
+        <f>G16*$B$4</f>
+        <v/>
+      </c>
+      <c r="I16" s="4">
+        <f>H16/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>9126_DARN</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Medium Rack Header - Hunt</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4911 10 90</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G17" s="4">
+        <f>D17*F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="4">
+        <f>G17*$B$4</f>
+        <v/>
+      </c>
+      <c r="I17" s="4">
+        <f>H17/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>9134_DARN</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Medium Rack Header - Run-Road 2021-1044</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4911 10 90</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G18" s="4">
+        <f>D18*F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="4">
+        <f>G18*$B$4</f>
+        <v/>
+      </c>
+      <c r="I18" s="4">
+        <f>H18/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>9160_DARN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dog Mill Header for Medium Racks</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4911 10 90</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G19" s="4">
+        <f>D19*F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="4">
+        <f>G19*$B$4</f>
+        <v/>
+      </c>
+      <c r="I19" s="4">
+        <f>H19/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>9176_DARN</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>DT Small Retail Rack Top &amp; Base</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>9403 20 80</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="G20" s="4">
+        <f>D20*F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="4">
+        <f>G20*$B$4</f>
+        <v/>
+      </c>
+      <c r="I20" s="4">
+        <f>H20/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>9177_DARN</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>DT Medium Retail Rack Top &amp; Base</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>9403 20 80</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" s="4">
+        <f>D21*F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="4">
+        <f>G21*$B$4</f>
+        <v/>
+      </c>
+      <c r="I21" s="4">
+        <f>H21/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>9147_DARN</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>DTV CREW Foot Form</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>9618 00 00</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G22" s="4">
+        <f>D22*F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="4">
+        <f>G22*$B$4</f>
+        <v/>
+      </c>
+      <c r="I22" s="4">
+        <f>H22/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>9158_DARN</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>DT OTC Foot Form</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>9618 00 00</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G23" s="4">
+        <f>D23*F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="4">
+        <f>G23*$B$4</f>
+        <v/>
+      </c>
+      <c r="I23" s="4">
+        <f>H23/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>9143_DARN</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>DTV Retail Rug</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5702 42 00</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G24" s="4">
+        <f>D24*F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="4">
+        <f>G24*$B$4</f>
+        <v/>
+      </c>
+      <c r="I24" s="4">
+        <f>H24/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>9178_DARN</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>DT Large Wings Only Retail Rack</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>9403 99 10</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="4">
+        <f>D25*F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="4">
+        <f>G25*$B$4</f>
+        <v/>
+      </c>
+      <c r="I25" s="4">
+        <f>H25/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>9055_DARN</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>TRY ON BOX SPRING 2021</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>9403 60 30</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" s="4">
+        <f>D26*F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="4">
+        <f>G26*$B$4</f>
+        <v/>
+      </c>
+      <c r="I26" s="4">
+        <f>H26/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>9006_DARN</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>DTV Metal Logo Sign</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>8310 00 00</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="4">
+        <f>D27*F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="4">
+        <f>G27*$B$4</f>
+        <v/>
+      </c>
+      <c r="I27" s="4">
+        <f>H27/$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>CELKEM</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6">
+        <f>SUM(D11:D27)</f>
+        <v/>
+      </c>
+      <c r="E28" s="6">
+        <f>SUM(E11:E27)</f>
+        <v/>
+      </c>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="7">
+        <f>SUM(G11:G27)</f>
+        <v/>
+      </c>
+      <c r="H28" s="7">
+        <f>SUM(H11:H27)</f>
+        <v/>
+      </c>
+      <c r="I28" s="7">
+        <f>SUM(I11:I27)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A8:I8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11">
+      <c r="A1" s="17">
         <f>== ZÁSILKA ===</f>
         <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Klient / příjemce (CZ): ADVENTURE GUY S.R.O., Radlická 348/142, Praha 5, 150 00, Česká republika</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Dodací adresa: Adventure Guy, Tomáš Man, Resin 6, Bezdružice 349 53, CZ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Odesílatel: Cabot Hosiery Mills (Darn Tough), 364 Whetstone Drive, PO Box 307, Northfield VT 05663, USA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Místo odeslání dle packing slipů: 6390 Commerce Ct, Groveport OH 43125, USA</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Faktury: 2026100076281 (objednávka 0010229255, PO „FW26 - PART 1-2“) a 2026100076288 (objednávka 0010242510, PO „POP 2026“), obě ze dne 15.7.2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Zákaznické č.: 9575 | Platební podmínky: N45, splatnost 28.8.2026</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Celkem: 266 ks, 1 622,00 USD (faktura 76281: 26 ks / 37,00 USD; faktura 76288: 240 ks / 1 585,00 USD)</t>
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Celkem: 266 ks, 134 kartonů, 1 622,00 USD, hrubá hmotnost 974 kg</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Množství na fakturách bylo odsouhlaseno kus po kuse proti oběma packing slipům – sedí přesně (26 ks i 240 ks).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr"/>
+      <c r="A10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="11">
+      <c r="A11" s="17">
+        <f>== ⚠️ HMOTNOSTI – METODA VÝPOČTU (nutno číst před podáním JSD) ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>DOLOŽENO: celková hrubá hmotnost 974 kg z BL. Toto je jediný doložený hmotnostní údaj.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>NEDOLOŽENO: rozpad hmotnosti na jednotlivé položky ani čistá hmotnost – v žádném dokladu nejsou.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Použitá metoda (list „Rozpočet hmotnosti“):</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>1. Ke každému SKU byla odhadnuta jednotková hrubá hmotnost podle druhu a materiálu zboží</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (ocelové stojany nejtěžší, plastové figuríny a papírové samolepky nejlehčí).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>2. Součet odhadů byl dorovnán přepočtovým faktorem tak, aby CELKEM přesně odpovídal 974 kg z BL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>3. Čistá hmotnost = hrubá / 1,12 (předpoklad 12 % na obaly). Faktor 1,12 odpovídá skutečně naměřenému</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   poměru 1,11992 ze zásilky Czech Healthcare 196652 – jde tedy o precedentovaný, nikoli vymyšlený údaj.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>→ Celková hrubá hmotnost je doložená. ROZPAD NA KÓDY KN JE KVALIFIKOVANÝ ODHAD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>→ Odhady jednotkových hmotností jsou ve sloupci F listu „Rozpočet hmotnosti“ a lze je přepsat –</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   vše se automaticky přepočítá a součet se vždy dorovná na 974 kg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>→ Rozpad nemá vliv na výši cla: žádný z kódů KN nemá specifické clo za kg, všechna cla jsou ad valorem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Nesprávný rozpad tedy neovlivní vyměřené clo, ale ovlivní správnost údajů v kol. 35/38 a statistiku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>⚠️ PALETY: 974 kg z BL je hrubá hmotnost zásilky u dopravce a pravděpodobně ZAHRNUJE palety.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>Při 134 kartonech půjde odhadem o 6–10 palet, tj. cca 120–250 kg. Pokud BL uvádí počet palet nebo tare,</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>je nutno palety odečíst – do kol. 35 patří hmotnost zboží včetně obalů, nikoli přepravní prostředky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>→ Ověřit u dopravce a případně upravit hodnotu v buňce B2 listu „Rozpočet hmotnosti“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>→ NEJČISTŠÍ ŘEŠENÍ: vyžádat od Darn Tough hmotnost po SKU nebo po kartonech (mají ji ve WMS,</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   z ní stavěli BL). Tím odpadne odhad úplně.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="17">
         <f>== ⚠️ PREFERENČNÍ VĚTA / COO – DŮLEŽITÉ ===</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>V žádném z dodaných dokladů (obě faktury ani oba packing slipy) NENÍ uvedena preferenční věta (prohlášení o preferenčním původu).</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Země původu deklarovaná na fakturách: US (Spojené státy) u všech položek.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>→ EU nemá se Spojenými státy dohodu o preferenčním obchodu, preferenční sazební zacházení tedy nelze uplatnit ani při doložení věty.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>→ Uplatní se běžné třetizemní (erga omnes) clo dle TARIC.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>Orientační sazby erga omnes (nutno ověřit v TARIC ke dni podání JSD):</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">   4911 10 90 – 0 %  |  8310 00 00 – 0 %  |  5702 42 00 – 8 %  |  9403 20 80 – 2,7 %  |  9403 99 10 – 2,7 %  |  9403 60 30 – 2,7 %  |  9618 00 00 – 1,7 %</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11">
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="17">
         <f>== CBAM ===</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>V zásilce NENÍ žádná položka podléhající CBAM.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>Žádný z kódů KN v této zásilce (4911 10 90, 5702 42 00, 8310 00 00, 9403 20 80, 9403 60 30, 9403 99 10, 9618 00 00) není uveden v příloze I nařízení o CBAM.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Pozor: některé položky ocel obsahují (prodejní stojany, „wings“, logo deska), ale jako hotové výrobky se zařazují do kap. 94 a 83, které do CBAM nespadají. CBAM se řídí kódem KN dovezeného zboží, nikoli materiálem.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>→ Do JSD se pro tuto zásilku žádný Y kód (Y128 / Y238 / Y137) neuvádí.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>⚠️ POZNÁMKA K REGISTRU CBAM: Příjemce ADVENTURE GUY S.R.O. NENÍ uveden v reference/CBAM_receivers_CZ.xlsx (list List1, sloupec Firma ani EORI).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>Pro tuto zásilku to nevadí (žádné CBAM zboží), ale pro budoucí zásilky s CBAM zbožím je potřeba firmu prověřit a do registru doplnit.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>Firma rovněž není mezi společnostmi využívajícími sdílený účet CBAM-CZ-2025-QGM67089385721.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11">
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17">
         <f>== ANTIDUMPING ===</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>Žádná z položek zásilky nepodléhá antidumpingovému clu – původ zboží je US a na uvedené kódy KN nejsou vůči USA zavedena antidumpingová opatření.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>Doporučeno ověřit v TARIC ke dni podání JSD.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11">
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="17">
         <f>== ⚠️ INCOTERM ===</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>Faktury uvádějí FREIGHT TERMS: EXW – ale BEZ uvedeného místa dodání (města).</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>Packing slipy uvádějí jako místo odeslání 6390 Commerce Ct, Groveport OH 43125 → pravděpodobně EXW Groveport, OH.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="18" t="inlineStr">
         <is>
           <t>Sídlo prodávajícího je však Northfield, VT (adresa na faktuře).</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>→ NUTNO POTVRDIT s odesílatelem, které místo k doložce EXW patří, před podáním JSD.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>→ Při EXW nejsou v ceně zahrnuty náklady na dopravu – do celní hodnoty je nutno připočíst dopravné a pojistné do místa vstupu do EU. Freight Charges na fakturách = 0,00 USD.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="11">
-        <f>== ⚠️ HMOTNOSTI – CHYBÍ ===</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>Čistá ani hrubá hmotnost NEJSOU uvedeny v žádném z dodaných dokladů (faktury, packing slipy ani sazební zařazení).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>Packing slipy uvádějí pouze počty kusů a čísla kartonů, nikoli hmotnosti.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>→ Nutno vyžádat od odesílatele nebo dopravce (LTL Carrier) – ideálně hmotnost po kartonech, aby šlo rozpočítat na jednotlivé kódy KN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>Sloupce v přehledu jsou ponechány a označeny „CHYBÍ“.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="11">
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="17">
         <f>== SLEVA ===</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
         <is>
           <t>Obchodní sleva se neuplatňuje – všechny řádky obou faktur mají DISCOUNT PERCENTAGE 0,00 % a sloupec DISCOUNT PRICE je prázdný.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
         <is>
           <t>Celní hodnota tedy odpovídá fakturované částce (Sub Total = Total Amount Due).</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="11">
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="17">
         <f>== MĚNA ===</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
         <is>
           <t>Faktury jsou v USD. Pro JSD přepočítat celním kurzem platným ke dni přijetí celního prohlášení.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="11">
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="17">
         <f>== SAZEBNÍ ZAŘAZENÍ – ZDROJ ===</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="18" t="inlineStr">
         <is>
           <t>Kódy KN převzaty z podkladu „Darn Tough TARIFF – sazební zařazení“ (listy 2026100076281 a 2026100076288), sloupce „Návrh HSC MW“ / „KN 2026“.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
         <is>
           <t>Popisy pro kolonku 31 JSD převzaty ze sloupce „Popis pro CP (kol. 31)“ téhož podkladu.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
         <is>
           <t>Dotazy na doplnění údajů byly zákazníkem zodpovězeny u SKU 9002, 9143, 9055, 9176, 9177, 9179 – odpovědi jsou zapracovány.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
         <is>
           <t>Zbývající nejistota: přesné složení rohože 9143 (zákazník uvádí, že složení nezná) – zařazení 5702 42 00 vychází z popisu „gumový spodek, potištěná syntetická nášlapná plocha, nevšívaná“.</t>
         </is>

--- a/output/HS_Code_Summary_Adventure_Guy_2026100076281_2026100076288.xlsx
+++ b/output/HS_Code_Summary_Adventure_Guy_2026100076281_2026100076288.xlsx
@@ -10,7 +10,8 @@
     <sheet name="HS Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Detail dle faktur" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Rozpočet hmotnosti" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dokumenty a poznámky" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Doplňkové MJ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dokumenty a poznámky" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -108,13 +110,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -124,6 +129,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,6 +161,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -518,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,11 +543,12 @@
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,25 +579,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Doplňková MJ – MTK (m²)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Čistá hmotnost (kg)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Hrubá hmotnost (kg)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Celní hodnota USD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Příznak</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TARIC / poznámka / CBAM / Antidumping</t>
         </is>
@@ -609,23 +632,28 @@
       <c r="E2" s="2" t="n">
         <v>143</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A2,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
         <v/>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A2,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
         <v/>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>1105</v>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>OVĚŘIT</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Na fakturách deklarováno pod US HTS 4908.90.5060 (obtisky), 3920.43.0000 (plast) a 4823.90.8600 (papír) – do JSD se uvádí KN 4911 10 90 (tiskoviny). Doplněno zákazníkem: jde o tištěné papírové samolepky, nikoli přenosové obtisky.</t>
         </is>
@@ -655,19 +683,24 @@
       <c r="E3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A3,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
         <v/>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A3,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
         <v/>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Faktura uvádí US HTS 9403.20.00.86. Doplněno zákazníkem: jde o kompletní volně stojící stojan (nikoli pouze část/nástavbu).</t>
         </is>
@@ -697,19 +730,24 @@
       <c r="E4" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A4,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
         <v/>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A4,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
         <v/>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -735,23 +773,27 @@
       <c r="E5" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="7">
+        <f>'Doplňkové MJ'!$G$6</f>
+        <v/>
+      </c>
+      <c r="G5" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A5,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
         <v/>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A5,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
         <v/>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>OVĚŘIT</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Faktura uvádí US HTS 5702.32.10.00. Přesné složení nášlapné plochy zákazník nezná – uvedeno: spodek gumový, nášlapná plocha syntetická, potištěná, nevšívaná. Zařazení 5702 42 00 z toho vychází; při odlišném složení ověřit.</t>
         </is>
@@ -781,19 +823,24 @@
       <c r="E6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A6,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
         <v/>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A6,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
         <v/>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Faktura uvádí US HTS 9403.20.00.86 (stojany); jde však o části nábytku z kovu → KN 9403 99 10.</t>
         </is>
@@ -823,19 +870,24 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A7,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
         <v/>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A7,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
         <v/>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Faktura uvádí US HTS 9403.60.0000. Doplněno zákazníkem: potištěná překližková bedna sloužící jako reklamní box na zkoušení ponožek v prodejně.</t>
         </is>
@@ -865,121 +917,142 @@
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A8,'Rozpočet hmotnosti'!$I$11:$I$27)</f>
         <v/>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="4">
         <f>SUMIF('Rozpočet hmotnosti'!$C$11:$C$27,A8,'Rozpočet hmotnosti'!$H$11:$H$27)</f>
         <v/>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>CELKEM</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr"/>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="n">
+      <c r="B9" s="8" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="n">
         <v>266</v>
       </c>
-      <c r="F9" s="7">
-        <f>SUM(F2:F8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="7">
+      <c r="F9" s="8">
+        <f>'Doplňkové MJ'!$G$6</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
         <f>SUM(G2:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="9">
+        <f>SUM(H2:H8)</f>
+        <v/>
+      </c>
+      <c r="I9" s="9" t="n">
         <v>1622</v>
       </c>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Legenda:</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr"/>
+      <c r="B11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>🟢 ZELENÁ</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Hmotnost dopočtena – viz list „Rozpočet hmotnosti“. Kotvena na hrubou hmotnost 974 kg z BL; rozpad na kódy KN je kvalifikovaný odhad.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>🟡 ŽLUTÁ</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Zařazení vyžaduje potvrzení – viz sloupec poznámky.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>CBAM</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>V zásilce NENÍ žádná položka podléhající CBAM – žádný z uvedených kódů KN není v příloze I nařízení CBAM. Detail viz list „Dokumenty a poznámky“.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Antidumping</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Žádná z položek nepodléhá antidumpingovému clu (původ US).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Incoterm</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>EXW – faktury neuvádějí místo dodání. Ověřit s odesílatelem (pravděpodobně EXW Groveport, OH). Viz poznámky.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Doplňková MJ</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>MTK (m²) požaduje pouze kód 5702 42 00 (kap. 57). U ostatních kódů se doplňková MJ neuvádí – viz list „Doplňkové MJ“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Sleva</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Obchodní sleva se neuplatňuje – všechny řádky obou faktur mají DISCOUNT PERCENTAGE 0,00 %.</t>
         </is>
@@ -1084,17 +1157,17 @@
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>4908.90.5060</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1135,7 +1208,7 @@
           <t>8310 00 00</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1176,7 +1249,7 @@
           <t>5702 42 00</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1217,7 +1290,7 @@
           <t>9403 99 10</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1258,7 +1331,7 @@
           <t>9403 60 30</t>
         </is>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1289,17 +1362,17 @@
       <c r="F7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>3920.43.0000</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1330,17 +1403,17 @@
       <c r="F8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>4823.90.8600</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1371,17 +1444,17 @@
       <c r="F9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>3920.43.0000</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1412,17 +1485,17 @@
       <c r="F10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>3920.43.0000</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1453,17 +1526,17 @@
       <c r="F11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>3920.43.0000</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1494,17 +1567,17 @@
       <c r="F12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>4823.90.8600</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1545,7 +1618,7 @@
           <t>5702 42 00</t>
         </is>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="5" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1586,7 +1659,7 @@
           <t>9618 00 00</t>
         </is>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="5" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1627,7 +1700,7 @@
           <t>9618 00 00</t>
         </is>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="5" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1658,17 +1731,17 @@
       <c r="F16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>3920.43.0000</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="5" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1709,7 +1782,7 @@
           <t>9403 20 80</t>
         </is>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="5" t="n">
         <v>200</v>
       </c>
     </row>
@@ -1750,7 +1823,7 @@
           <t>9403 20 80</t>
         </is>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="5" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1791,7 +1864,7 @@
           <t>9403 99 10</t>
         </is>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="5" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1822,50 +1895,50 @@
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>4908.90.5060</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>4911 10 90</t>
         </is>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I20" s="5" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>CELKEM</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="n">
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="8" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="8" t="n">
         <v>266</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="8" t="n">
         <v>134</v>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="7" t="n">
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="9" t="n">
         <v>1622</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Žlutě: US HTS kód na faktuře se liší od kódu KN použitého pro dovozní JSD (běžná odchylka US HTS vs. EU KN).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Kartony načteny z packing slipů podle jedinečných čísel SSCC – celkem 134 kartonů (7 + 127).</t>
         </is>
@@ -1897,67 +1970,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>ROZPOČET HMOTNOSTI NA KÓDY KN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Celková hrubá hmotnost dle BL (kg)</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n">
+      <c r="B2" s="15" t="n">
         <v>974</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Součet odhadů (kg)</t>
         </is>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="15">
         <f>SUM(G11:G27)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Přepočtový faktor (BL / součet odhadů)</t>
         </is>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="16">
         <f>B2/B3</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Faktor obalu (hrubá / čistá)</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="15" t="n">
         <v>1.12</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Celková čistá hmotnost (kg)</t>
         </is>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="15">
         <f>SUM(I11:I27)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>VSTUPNÍ ÚDAJ K ÚPRAVĚ: sloupec F (odhad jednotkové hmotnosti). Přepiš hodnoty podle skutečnosti – součet se vždy automaticky dorovná na hrubou hmotnost 974 kg z BL.</t>
         </is>
@@ -2032,18 +2105,18 @@
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="18" t="n">
         <v>0.15</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <f>D11*F11</f>
         <v/>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="5">
         <f>G11*$B$4</f>
         <v/>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="5">
         <f>H11/$B$5</f>
         <v/>
       </c>
@@ -2070,18 +2143,18 @@
       <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <f>D12*F12</f>
         <v/>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <f>G12*$B$4</f>
         <v/>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="5">
         <f>H12/$B$5</f>
         <v/>
       </c>
@@ -2108,18 +2181,18 @@
       <c r="E13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="5">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="5">
         <f>G13*$B$4</f>
         <v/>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="5">
         <f>H13/$B$5</f>
         <v/>
       </c>
@@ -2146,18 +2219,18 @@
       <c r="E14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <f>D14*F14</f>
         <v/>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="5">
         <f>G14*$B$4</f>
         <v/>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="5">
         <f>H14/$B$5</f>
         <v/>
       </c>
@@ -2184,18 +2257,18 @@
       <c r="E15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="5">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="5">
         <f>G15*$B$4</f>
         <v/>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="5">
         <f>H15/$B$5</f>
         <v/>
       </c>
@@ -2222,18 +2295,18 @@
       <c r="E16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <f>D16*F16</f>
         <v/>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="5">
         <f>G16*$B$4</f>
         <v/>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="5">
         <f>H16/$B$5</f>
         <v/>
       </c>
@@ -2260,18 +2333,18 @@
       <c r="E17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="5">
         <f>D17*F17</f>
         <v/>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="5">
         <f>G17*$B$4</f>
         <v/>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="5">
         <f>H17/$B$5</f>
         <v/>
       </c>
@@ -2298,18 +2371,18 @@
       <c r="E18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="5">
         <f>D18*F18</f>
         <v/>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="5">
         <f>G18*$B$4</f>
         <v/>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="5">
         <f>H18/$B$5</f>
         <v/>
       </c>
@@ -2336,18 +2409,18 @@
       <c r="E19" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="5">
         <f>D19*F19</f>
         <v/>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="5">
         <f>G19*$B$4</f>
         <v/>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="5">
         <f>H19/$B$5</f>
         <v/>
       </c>
@@ -2374,18 +2447,18 @@
       <c r="E20" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="5">
         <f>D20*F20</f>
         <v/>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="5">
         <f>G20*$B$4</f>
         <v/>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="5">
         <f>H20/$B$5</f>
         <v/>
       </c>
@@ -2412,18 +2485,18 @@
       <c r="E21" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="5">
         <f>D21*F21</f>
         <v/>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="5">
         <f>G21*$B$4</f>
         <v/>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="5">
         <f>H21/$B$5</f>
         <v/>
       </c>
@@ -2450,18 +2523,18 @@
       <c r="E22" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="18" t="n">
         <v>0.6</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="5">
         <f>D22*F22</f>
         <v/>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="5">
         <f>G22*$B$4</f>
         <v/>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="5">
         <f>H22/$B$5</f>
         <v/>
       </c>
@@ -2488,18 +2561,18 @@
       <c r="E23" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="18" t="n">
         <v>0.8</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="5">
         <f>D23*F23</f>
         <v/>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="5">
         <f>G23*$B$4</f>
         <v/>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="5">
         <f>H23/$B$5</f>
         <v/>
       </c>
@@ -2526,18 +2599,18 @@
       <c r="E24" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="5">
         <f>D24*F24</f>
         <v/>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="5">
         <f>G24*$B$4</f>
         <v/>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="5">
         <f>H24/$B$5</f>
         <v/>
       </c>
@@ -2564,18 +2637,18 @@
       <c r="E25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="5">
         <f>D25*F25</f>
         <v/>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="5">
         <f>G25*$B$4</f>
         <v/>
       </c>
-      <c r="I25" s="4">
+      <c r="I25" s="5">
         <f>H25/$B$5</f>
         <v/>
       </c>
@@ -2602,18 +2675,18 @@
       <c r="E26" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="5">
         <f>D26*F26</f>
         <v/>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="5">
         <f>G26*$B$4</f>
         <v/>
       </c>
-      <c r="I26" s="4">
+      <c r="I26" s="5">
         <f>H26/$B$5</f>
         <v/>
       </c>
@@ -2640,48 +2713,48 @@
       <c r="E27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="5">
         <f>D27*F27</f>
         <v/>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="5">
         <f>G27*$B$4</f>
         <v/>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="5">
         <f>H27/$B$5</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>CELKEM</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6">
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8">
         <f>SUM(D11:D27)</f>
         <v/>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="8">
         <f>SUM(E11:E27)</f>
         <v/>
       </c>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="7">
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="9">
         <f>SUM(G11:G27)</f>
         <v/>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="9">
         <f>SUM(H11:H27)</f>
         <v/>
       </c>
-      <c r="I28" s="7">
+      <c r="I28" s="9">
         <f>SUM(I11:I27)</f>
         <v/>
       </c>
@@ -2700,478 +2773,994 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A76"/>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>DOPLŇKOVÉ MĚRNÉ JEDNOTKY (Helios – pole „Množství v MJ“)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>MTK = metr čtvereční (m²). Doplňkovou MJ vyžaduje z této zásilky POUZE kód 5702 42 00 – celá kapitola 57 (koberce) se vykazuje v m². U ostatních kódů zásilky Helios pole „Množství v MJ“ nevyplní, protože pro ně sazebník doplňkovou jednotku nestanoví.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>HS kód (KN)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Požadovaná MJ</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Množství (ks)</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Šířka 1 ks (m)</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Délka 1 ks (m)</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Plocha 1 ks (m²)</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>CELKEM MTK (m²)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>5702 42 00</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>MTK (m²)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="3">
+        <f>IF(OR(D6="",E6=""),"DOPLNIT",ROUND(D6*E6,4))</f>
+        <v/>
+      </c>
+      <c r="G6" s="23">
+        <f>IF(OR(D6="",E6=""),"DOPLNIT",ROUND(C6*D6*E6,2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>4911 10 90</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>8310 00 00</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>9403 20 80</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>9403 60 30</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>9403 99 10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>9618 00 00</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ ŽLUTÁ POLE (D6, E6) = VSTUP. Zadej rozměr jedné rohože v metrech; MTK se dopočítá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rozměry rohože NEJSOU v žádném z dodaných dokladů (faktury, packing slipy, sazební zařazení) – nutno vyžádat od Darn Tough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Orientační převod běžných velikostí (jen pro kontrolu, NE k vyplnění):</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Velikost</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Šířka (m)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Délka (m)</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Plocha 1 ks (m²)</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>32 ks celkem (m²)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>2 ft × 3 ft</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="n">
+        <v>0.6096</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>0.9144</v>
+      </c>
+      <c r="D19" s="26">
+        <f>ROUND(B19*C19,4)</f>
+        <v/>
+      </c>
+      <c r="E19" s="25">
+        <f>ROUND(32*B19*C19,2)</f>
+        <v/>
+      </c>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>3 ft × 5 ft</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="n">
+        <v>0.9144</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="D20" s="26">
+        <f>ROUND(B20*C20,4)</f>
+        <v/>
+      </c>
+      <c r="E20" s="25">
+        <f>ROUND(32*B20*C20,2)</f>
+        <v/>
+      </c>
+      <c r="F20" s="24" t="n"/>
+      <c r="G20" s="24" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>4 ft × 6 ft</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="n">
+        <v>1.2192</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>1.8288</v>
+      </c>
+      <c r="D21" s="26">
+        <f>ROUND(B21*C21,4)</f>
+        <v/>
+      </c>
+      <c r="E21" s="25">
+        <f>ROUND(32*B21*C21,2)</f>
+        <v/>
+      </c>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>60 × 90 cm</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D22" s="26">
+        <f>ROUND(B22*C22,4)</f>
+        <v/>
+      </c>
+      <c r="E22" s="25">
+        <f>ROUND(32*B22*C22,2)</f>
+        <v/>
+      </c>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="24" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>90 × 150 cm</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D23" s="26">
+        <f>ROUND(B23*C23,4)</f>
+        <v/>
+      </c>
+      <c r="E23" s="25">
+        <f>ROUND(32*B23*C23,2)</f>
+        <v/>
+      </c>
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>120 × 180 cm</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D24" s="26">
+        <f>ROUND(B24*C24,4)</f>
+        <v/>
+      </c>
+      <c r="E24" s="25">
+        <f>ROUND(32*B24*C24,2)</f>
+        <v/>
+      </c>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Kontrola věrohodnosti: gumou podložená potištěná rohož váží zhruba 3–4 kg/m². Odhadovaná čistá hmotnost 1 ks je cca 3,96 kg → odpovídá řádově 1,0–1,3 m² na kus. Až budou známy skutečné rozměry, ověř, že tomuto řádu odpovídají.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ NEVYPLŇUJ do pole „Množství v MJ“ čistou hmotnost – MTK je plocha v m², nikoli kg. Jsou to dvě různé veličiny a Helios je nekontroluje proti sobě.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A26:G27"/>
+    <mergeCell ref="A3:G4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17">
+      <c r="A1" s="19">
         <f>== ZÁSILKA ===</f>
         <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Klient / příjemce (CZ): ADVENTURE GUY S.R.O., Radlická 348/142, Praha 5, 150 00, Česká republika</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Dodací adresa: Adventure Guy, Tomáš Man, Resin 6, Bezdružice 349 53, CZ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Odesílatel: Cabot Hosiery Mills (Darn Tough), 364 Whetstone Drive, PO Box 307, Northfield VT 05663, USA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Místo odeslání dle packing slipů: 6390 Commerce Ct, Groveport OH 43125, USA</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Faktury: 2026100076281 (objednávka 0010229255, PO „FW26 - PART 1-2“) a 2026100076288 (objednávka 0010242510, PO „POP 2026“), obě ze dne 15.7.2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Zákaznické č.: 9575 | Platební podmínky: N45, splatnost 28.8.2026</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Celkem: 266 ks, 134 kartonů, 1 622,00 USD, hrubá hmotnost 974 kg</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Množství na fakturách bylo odsouhlaseno kus po kuse proti oběma packing slipům – sedí přesně (26 ks i 240 ks).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr"/>
+      <c r="A10" s="20" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="17">
+      <c r="A11" s="19">
         <f>== ⚠️ HMOTNOSTI – METODA VÝPOČTU (nutno číst před podáním JSD) ===</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>DOLOŽENO: celková hrubá hmotnost 974 kg z BL. Toto je jediný doložený hmotnostní údaj.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>NEDOLOŽENO: rozpad hmotnosti na jednotlivé položky ani čistá hmotnost – v žádném dokladu nejsou.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr"/>
+      <c r="A14" s="20" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Použitá metoda (list „Rozpočet hmotnosti“):</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>1. Ke každému SKU byla odhadnuta jednotková hrubá hmotnost podle druhu a materiálu zboží</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">   (ocelové stojany nejtěžší, plastové figuríny a papírové samolepky nejlehčí).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2. Součet odhadů byl dorovnán přepočtovým faktorem tak, aby CELKEM přesně odpovídal 974 kg z BL.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>3. Čistá hmotnost = hrubá / 1,12 (předpoklad 12 % na obaly). Faktor 1,12 odpovídá skutečně naměřenému</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">   poměru 1,11992 ze zásilky Czech Healthcare 196652 – jde tedy o precedentovaný, nikoli vymyšlený údaj.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr"/>
+      <c r="A21" s="20" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>→ Celková hrubá hmotnost je doložená. ROZPAD NA KÓDY KN JE KVALIFIKOVANÝ ODHAD.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>→ Odhady jednotkových hmotností jsou ve sloupci F listu „Rozpočet hmotnosti“ a lze je přepsat –</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">   vše se automaticky přepočítá a součet se vždy dorovná na 974 kg.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>→ Rozpad nemá vliv na výši cla: žádný z kódů KN nemá specifické clo za kg, všechna cla jsou ad valorem.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">   Nesprávný rozpad tedy neovlivní vyměřené clo, ale ovlivní správnost údajů v kol. 35/38 a statistiku.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr"/>
+      <c r="A27" s="20" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>⚠️ PALETY: 974 kg z BL je hrubá hmotnost zásilky u dopravce a pravděpodobně ZAHRNUJE palety.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Při 134 kartonech půjde odhadem o 6–10 palet, tj. cca 120–250 kg. Pokud BL uvádí počet palet nebo tare,</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>je nutno palety odečíst – do kol. 35 patří hmotnost zboží včetně obalů, nikoli přepravní prostředky.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>→ Ověřit u dopravce a případně upravit hodnotu v buňce B2 listu „Rozpočet hmotnosti“.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr"/>
+      <c r="A32" s="20" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>→ NEJČISTŠÍ ŘEŠENÍ: vyžádat od Darn Tough hmotnost po SKU nebo po kartonech (mají ji ve WMS,</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">   z ní stavěli BL). Tím odpadne odhad úplně.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr"/>
+      <c r="A35" s="20" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="17">
+      <c r="A36" s="19">
+        <f>== ⚠️ DOPLŇKOVÁ MJ – MTK (pole „Množství v MJ“ v Heliosu) ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>MTK = metr čtvereční. Doplňkovou MJ vyžaduje z této zásilky POUZE kód 5702 42 00 (rohože) – celá kap. 57 se vykazuje v m².</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>U ostatních šesti kódů zásilky (4911 10 90, 8310 00 00, 9403 20 80, 9403 60 30, 9403 99 10, 9618 00 00) sazebník doplňkovou MJ nestanoví –</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>Helios pole „Množství v MJ“ pro ně nenabídne. Pokud jej u některého kódu nabídne, řídit se Heliosem (tahá MJ přímo ze sazebníku).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>⚠️ ÚDAJ CHYBÍ: rozměry rohože (9143 DTV Retail Rug, 32 ks) NEJSOU v žádném z dodaných dokladů – ani rozměr, ani plocha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>Prohledány obě faktury, oba packing slipy i sazební zařazení: žádný údaj o rozměru, ploše ani m².</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>→ Vyžádat od Darn Tough rozměr jedné rohože a zadat jej do listu „Doplňkové MJ“, buňky D6 a E6. MTK se dopočítá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>→ MTK = počet kusů × plocha 1 ks. Při 32 ks a např. rohoži 90 × 150 cm to je 32 × 1,35 = 43,20 m².</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>⚠️ Do pole „Množství v MJ“ NEPATŘÍ hmotnost. MTK je plocha v m², čistá hmotnost je v kg – dvě různé veličiny.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Helios tyto dvě hodnoty proti sobě nekontroluje, chyba tedy projde až do statistiky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>Clo to neovlivní (5702 42 00 má clo 8 % ad valorem, nikoli za m²), ale jde o nesprávný údaj v celním prohlášení.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="19">
         <f>== ⚠️ PREFERENČNÍ VĚTA / COO – DŮLEŽITÉ ===</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>V žádném z dodaných dokladů (obě faktury ani oba packing slipy) NENÍ uvedena preferenční věta (prohlášení o preferenčním původu).</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>Země původu deklarovaná na fakturách: US (Spojené státy) u všech položek.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>→ EU nemá se Spojenými státy dohodu o preferenčním obchodu, preferenční sazební zacházení tedy nelze uplatnit ani při doložení věty.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="19" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>→ Uplatní se běžné třetizemní (erga omnes) clo dle TARIC.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>Orientační sazby erga omnes (nutno ověřit v TARIC ke dni podání JSD):</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">   4911 10 90 – 0 %  |  8310 00 00 – 0 %  |  5702 42 00 – 8 %  |  9403 20 80 – 2,7 %  |  9403 99 10 – 2,7 %  |  9403 60 30 – 2,7 %  |  9618 00 00 – 1,7 %</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="18" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="17">
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="19">
         <f>== CBAM ===</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>V zásilce NENÍ žádná položka podléhající CBAM.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
         <is>
           <t>Žádný z kódů KN v této zásilce (4911 10 90, 5702 42 00, 8310 00 00, 9403 20 80, 9403 60 30, 9403 99 10, 9618 00 00) není uveden v příloze I nařízení o CBAM.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="20" t="inlineStr">
         <is>
           <t>Pozor: některé položky ocel obsahují (prodejní stojany, „wings“, logo deska), ale jako hotové výrobky se zařazují do kap. 94 a 83, které do CBAM nespadají. CBAM se řídí kódem KN dovezeného zboží, nikoli materiálem.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="19" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="21" t="inlineStr">
         <is>
           <t>→ Do JSD se pro tuto zásilku žádný Y kód (Y128 / Y238 / Y137) neuvádí.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="18" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="19" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="20" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>⚠️ POZNÁMKA K REGISTRU CBAM: Příjemce ADVENTURE GUY S.R.O. NENÍ uveden v reference/CBAM_receivers_CZ.xlsx (list List1, sloupec Firma ani EORI).</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t>Pro tuto zásilku to nevadí (žádné CBAM zboží), ale pro budoucí zásilky s CBAM zbožím je potřeba firmu prověřit a do registru doplnit.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="20" t="inlineStr">
         <is>
           <t>Firma rovněž není mezi společnostmi využívajícími sdílený účet CBAM-CZ-2025-QGM67089385721.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="18" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="17">
+    <row r="67">
+      <c r="A67" s="20" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="19">
         <f>== ANTIDUMPING ===</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>Žádná z položek zásilky nepodléhá antidumpingovému clu – původ zboží je US a na uvedené kódy KN nejsou vůči USA zavedena antidumpingová opatření.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="20" t="inlineStr">
         <is>
           <t>Doporučeno ověřit v TARIC ke dni podání JSD.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="18" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="17">
+    <row r="71">
+      <c r="A71" s="20" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="19">
         <f>== ⚠️ INCOTERM ===</f>
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
         <is>
           <t>Faktury uvádějí FREIGHT TERMS: EXW – ale BEZ uvedeného místa dodání (města).</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="18" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="20" t="inlineStr">
         <is>
           <t>Packing slipy uvádějí jako místo odeslání 6390 Commerce Ct, Groveport OH 43125 → pravděpodobně EXW Groveport, OH.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="18" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="20" t="inlineStr">
         <is>
           <t>Sídlo prodávajícího je však Northfield, VT (adresa na faktuře).</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="19" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="21" t="inlineStr">
         <is>
           <t>→ NUTNO POTVRDIT s odesílatelem, které místo k doložce EXW patří, před podáním JSD.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="19" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="21" t="inlineStr">
         <is>
           <t>→ Při EXW nejsou v ceně zahrnuty náklady na dopravu – do celní hodnoty je nutno připočíst dopravné a pojistné do místa vstupu do EU. Freight Charges na fakturách = 0,00 USD.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="18" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="17">
+    <row r="78">
+      <c r="A78" s="20" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="19">
         <f>== SLEVA ===</f>
         <v/>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="18" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>Obchodní sleva se neuplatňuje – všechny řádky obou faktur mají DISCOUNT PERCENTAGE 0,00 % a sloupec DISCOUNT PRICE je prázdný.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="18" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="20" t="inlineStr">
         <is>
           <t>Celní hodnota tedy odpovídá fakturované částce (Sub Total = Total Amount Due).</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="18" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="17">
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="19">
         <f>== MĚNA ===</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="18" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
         <is>
           <t>Faktury jsou v USD. Pro JSD přepočítat celním kurzem platným ke dni přijetí celního prohlášení.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="18" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="17">
+    <row r="85">
+      <c r="A85" s="20" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="19">
         <f>== SAZEBNÍ ZAŘAZENÍ – ZDROJ ===</f>
         <v/>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="18" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="20" t="inlineStr">
         <is>
           <t>Kódy KN převzaty z podkladu „Darn Tough TARIFF – sazební zařazení“ (listy 2026100076281 a 2026100076288), sloupce „Návrh HSC MW“ / „KN 2026“.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="18" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="20" t="inlineStr">
         <is>
           <t>Popisy pro kolonku 31 JSD převzaty ze sloupce „Popis pro CP (kol. 31)“ téhož podkladu.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="18" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="20" t="inlineStr">
         <is>
           <t>Dotazy na doplnění údajů byly zákazníkem zodpovězeny u SKU 9002, 9143, 9055, 9176, 9177, 9179 – odpovědi jsou zapracovány.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="18" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="20" t="inlineStr">
         <is>
           <t>Zbývající nejistota: přesné složení rohože 9143 (zákazník uvádí, že složení nezná) – zařazení 5702 42 00 vychází z popisu „gumový spodek, potištěná syntetická nášlapná plocha, nevšívaná“.</t>
         </is>
